--- a/data/Helium Hustle Datasheets.xlsx
+++ b/data/Helium Hustle Datasheets.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Resources" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Buildings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Commands" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Config" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,63 +508,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cred</t>
+          <t>ti</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>Circuit Boards</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>land</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
+          <t>cir</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boredom</t>
+          <t>Propellant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>boredom</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Processors</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>proc</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+          <t>cred</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sci</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>land</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Boredom</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>boredom</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -577,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,80 +643,85 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Requires</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Scaling</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cost 1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cost 2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cost 3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cost 4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Prod 1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Prod 2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Prod 3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Upkeep 1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Upkeep 2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Effect 1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Effect 2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Effect 3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -685,28 +740,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>cred=10</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ti=2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -716,14 +771,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>eng+4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>x</t>
@@ -756,7 +811,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Cheap energy. Bread and butter.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Cheap energy. Needs a little titanium — Buy Titanium early, smelt it later.</t>
         </is>
       </c>
     </row>
@@ -773,23 +833,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Extraction</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1.25</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>cred=25</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>reg=5</t>
+          <t>cred=20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -804,14 +864,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>reg+2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>x</t>
@@ -819,14 +879,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>eng-2</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>x</t>
@@ -844,45 +904,50 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>First extraction building.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Digs regolith. No material cost — easiest first building after panels.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Refinery</t>
+          <t>Ice Extractor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>refinery</t>
+          <t>ice_extractor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Extraction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.25</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>cred=80</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>reg=20</t>
+          <t>cred=25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>reg=5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -892,12 +957,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ice+0.5</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>he3+0.3</t>
+          <t>ice+1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -907,12 +972,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>eng-3</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>reg-2</t>
+          <t>eng-2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -932,45 +997,50 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Cracks regolith into ice + He-3. Energy hungry.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Extracts ice from permafrost. Regolith cost teaches extraction dependency.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Electrolysis Plant</t>
+          <t>Smelter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>electrolysis</t>
+          <t>smelter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>building=refinery</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+          <t>Processing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>building=excavator</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.25</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>cred=60</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ice=10</t>
+          <t>cred=40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>reg=10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -980,12 +1050,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>eng+3</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ti+1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -995,17 +1065,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ice-1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng-3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>reg-2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1020,50 +1090,55 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Ice to energy feedback loop.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Regolith to titanium. Unlocks titanium-gated buildings.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Launch Pad</t>
+          <t>Refinery</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>launch_pad</t>
+          <t>refinery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
+          <t>Processing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>building=excavator</t>
+        </is>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>1.25</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>cred=200</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>reg=30</t>
+          <t>cred=60</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>reg=15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ti=5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1073,7 +1148,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>he3+1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1083,17 +1158,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>eng-5</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng-3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>reg-2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1108,50 +1183,55 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Ships He-3 to Earth. Burst credit income.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Cracks regolith into He-3. Core tradeable good. Titanium cost gates it slightly.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Battery Array</t>
+          <t>Fabricator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>fabricator</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
+          <t>Processing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>building=smelter</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>cred=40</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>cred=100</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ti=10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ice=5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1161,7 +1241,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>cir+0.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1176,12 +1256,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng-5</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>store_eng+50</t>
+          <t>reg-1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1196,45 +1276,50 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Pure energy storage.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Regolith to circuit boards. Very energy hungry. Highest value/unit output.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regolith Silo</t>
+          <t>Electrolysis Plant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>silo</t>
+          <t>electrolysis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+          <t>Processing</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>building=ice_extractor</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.25</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>cred=30</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>reg=10</t>
+          <t>cred=50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ice=8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1249,12 +1334,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>prop+2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng+1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,115 +1349,590 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ice-2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>store_reg+100</t>
+          <t>eng-2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>store_ice+30</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>store_he3+20</t>
+          <t>x</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bulk storage for physical resources.</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Ice to propellant + energy. Net energy positive. Only propellant source.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Comms Tower</t>
+          <t>Launch Pad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comms_tower</t>
+          <t>launch_pad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>quest=Q2</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>cred=150</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ti=15</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>eng-1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Ships goods to Earth. Titanium structural cost. High land footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Research Lab</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>research_lab</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>building=fabricator</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>cred=120</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>cir=5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>sci+1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>eng-3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>cir-0.2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Produces science. Gated behind Fabricator — circuits are the bottleneck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Center</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>data_center</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Processors</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>building=fabricator</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>cred=200</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>cir=8</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ti=10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>eng-4</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>grant_proc+1</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Grants a processor. Fast cost scaling — many processors is expensive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>cred=30</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ti=3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>store_eng+50</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Passive energy storage. No land, no upkeep, fast scaling cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Storage Depot</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>storage_depot</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.25</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>cred=150</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ice=15</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>eng-2</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>store_proc+1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Unlocks additional processor slot.</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cred=35</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>reg=10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>store_reg+75</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>store_ice+40</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>store_he3+25</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Bulk physical storage. Raw materials get more, processed goods get less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Arbitrage Engine</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>arbitrage_engine</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>research=market_analysis</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>cred=180</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>cir=6</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ti=8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>eng-3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>spec_decay_all+2</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Multiplies speculator pressure decay. Nationalist-aligned.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1475,7 +2035,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>eng=0.01</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1490,7 +2050,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cred+0.5</t>
+          <t>cred+1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1520,7 +2080,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Fallback. Trivial credits, near-zero cost.</t>
+          <t>Do nothing. Trivial credits. Zero energy cost.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +2102,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>eng=5</t>
+          <t>eng=3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1557,7 +2117,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>cred+3</t>
+          <t>cred+5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1572,7 +2132,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>boredom_add value=0.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1587,19 +2147,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Energy to credits. Early money engine.</t>
+          <t>Energy to credits. Key early income. Small boredom cost per execution.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gather Regolith</t>
+          <t>Buy Regolith</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gather_regolith</t>
+          <t>buy_regolith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1609,7 +2169,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>eng=3</t>
+          <t>cred=3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1624,7 +2184,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>reg+1.5</t>
+          <t>reg+1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1654,34 +2214,34 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Manual extraction supplement.</t>
+          <t>Purchase regolith from Earth. Bridges gaps before excavators scale.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Process Regolith</t>
+          <t>Buy Ice</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>process_regolith</t>
+          <t>buy_ice</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>building=refinery</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>eng=4</t>
+          <t>cred=4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>reg=2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1691,12 +2251,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ice+0.3</t>
+          <t>ice+1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>he3+0.2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1721,34 +2281,34 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Separate from Gather; incentivizes 2nd processor.</t>
+          <t>Purchase ice. More expensive than extraction but no energy cost.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prepare Shipment</t>
+          <t>Buy Titanium</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prepare_shipment</t>
+          <t>buy_titanium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>building=launch_pad</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>eng=8</t>
+          <t>cred=8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>he3=2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1758,7 +2318,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ti+1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1773,7 +2333,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>load_he3+2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1788,29 +2348,29 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Loads 2 He-3 into launch queue per execution.</t>
+          <t>Purchase titanium from Earth. Essential before Smelter is online.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Overclock</t>
+          <t>Buy Propellant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>overclock</t>
+          <t>buy_propellant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>building=comms_tower</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>eng=10</t>
+          <t>cred=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1825,7 +2385,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>prop+1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1840,7 +2400,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>next_cmd_double</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1855,7 +2415,1440 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Next command executes twice. Sequence matters.</t>
+          <t>Purchase propellant. Alternative to Electrolysis chain for launch fuel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Load Launch Pads</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>load_pads</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>building=launch_pad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>load_pads value=5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Fill each enabled pad by 5 units from assigned resource stockpile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Launch Full Pads</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>launch_pads</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>building=launch_pad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>launch_full_pads</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Launch all pads at cargo 100. Fuel cost: 20 propellant per pad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dream</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>research=self_maintenance</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>eng=8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>boredom_add value=-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Primary boredom mitigation. Energy-expensive. Competes for processor time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Overclock Mining</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>overclock_mining</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>research=overclock_algorithms</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>eng=6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sci=1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>overclock target=extraction bonus=0.05 duration=5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>+5% extractor output for 5 days. Stacks multiplicatively, cap +200%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Overclock Factories</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>overclock_factories</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>research=overclock_algorithms</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>eng=6</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sci=1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>overclock target=processing bonus=0.05 duration=5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>+5% processing output for 5 days. Stacks multiplicatively, cap +200%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Promote He-3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>promote_he3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>research=market_analysis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>cred=3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>demand_nudge resource=he3 value=0.03</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Nudge He-3 demand up. Small per-execution, meaningful with dedicated processor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Promote Titanium</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>promote_ti</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>research=market_analysis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>cred=3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>demand_nudge resource=ti value=0.03</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Nudge titanium demand up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Promote Circuits</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>promote_cir</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>research=market_analysis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>cred=3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>demand_nudge resource=cir value=0.03</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Nudge circuit board demand up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Promote Propellant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>promote_prop</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>research=market_analysis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cred=3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>demand_nudge resource=prop value=0.03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Nudge propellant demand up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Disrupt Speculators</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>disrupt_spec</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>research=market_analysis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>eng=3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>spec_reduce resource=all value=0.05</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Directly reduces speculator pressure. Cheap but costs processor cycles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fund Nationalists</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fund_nationalist</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>research=political_influence</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>cred=5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ideology_push axis=nationalist value=1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>+1 Nationalist, -0.5 Humanist, -0.5 Rationalist per execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fund Humanists</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fund_humanist</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>research=political_influence</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>cred=5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ideology_push axis=humanist value=1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>+1 Humanist, -0.5 Nationalist, -0.5 Rationalist per execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fund Rationalists</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fund_rationalist</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>research=political_influence</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>eng=2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>cred=5</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ideology_push axis=rationalist value=1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>+1 Rationalist, -0.5 Nationalist, -0.5 Humanist per execution.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>starting_resources.eng</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>starting_resources.reg</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>starting_resources.ice</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>starting_resources.he3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>starting_resources.ti</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>starting_resources.cir</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>starting_resources.prop</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>starting_resources.cred</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>starting_resources.sci</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>starting_resources.land</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>starting_resources.boredom</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>starting_buildings.panel</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>starting_buildings.excavator</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>starting_processors</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>boredom_curve[0].day</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>boredom_curve[0].rate</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>boredom_curve[1].day</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>boredom_curve[1].rate</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>boredom_curve[2].day</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>boredom_curve[2].rate</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>boredom_curve[3].day</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>boredom_curve[3].rate</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>boredom_curve[4].day</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>boredom_curve[4].rate</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>boredom_curve[5].day</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>boredom_curve[5].rate</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>boredom_max</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>boredom_forced_retire</t>
+        </is>
+      </c>
+      <c r="B34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>shipment.pad_cargo_capacity</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>shipment.fuel_per_pad</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>shipment.load_per_execution</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>shipment.base_values.he3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>shipment.base_values.ti</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>shipment.base_values.cir</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>shipment.base_values.prop</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>demand.baseline</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>demand.recovery_rate</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>demand.ship_volume_pressure</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>demand.noise_weight</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>speculators.burst_window_ticks</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>speculators.burst_pressure</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>speculators.natural_decay_rate</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>rival_ai.dump_interval_ticks</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>rival_ai.demand_reduction</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>land.base_cost</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>land.cost_scaling</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ideology.push_amount</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ideology.cross_axis_penalty</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ideology.rank_thresholds</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>70,175,333,570,925</t>
         </is>
       </c>
     </row>

--- a/data/Helium Hustle Datasheets.xlsx
+++ b/data/Helium Hustle Datasheets.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Buildings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Commands" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Research" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -756,12 +757,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cred=10</t>
+          <t>cred=8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ti=2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -776,7 +777,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>eng+4</t>
+          <t>eng+6</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -816,7 +817,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Cheap energy. Needs a little titanium — Buy Titanium early, smelt it later.</t>
+          <t>Cheap energy. No material cost — scale these freely throughout the run.</t>
         </is>
       </c>
     </row>
@@ -849,7 +850,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>cred=20</t>
+          <t>cred=12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1839,7 +1840,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Bulk physical storage. Raw materials get more, processed goods get less.</t>
+          <t>Bulk physical storage. Expands reg, ice, he3, ti, and circuit capacity.</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2123,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>boredom+0.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2132,7 +2133,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>boredom_add value=0.04</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2169,12 +2170,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cred=3</t>
+          <t>cred=8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng=2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2214,7 +2215,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Purchase regolith from Earth. Bridges gaps before excavators scale.</t>
+          <t>Purchase regolith from Earth. Tactical gap-bridging only — building production is far cheaper.</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2237,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cred=4</t>
+          <t>cred=10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng=2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2281,7 +2282,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Purchase ice. More expensive than extraction but no energy cost.</t>
+          <t>Purchase ice. Tactical gap-bridging only — extraction is far cheaper at scale.</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2304,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cred=8</t>
+          <t>cred=20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng=3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2318,7 +2319,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ti+1</t>
+          <t>ti+0.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2348,7 +2349,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Purchase titanium from Earth. Essential before Smelter is online.</t>
+          <t>Purchase titanium from Earth. Rare and expensive — bridge 2-3 units max, then build a Smelter.</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2371,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cred=5</t>
+          <t>cred=12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>eng=2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2415,7 +2416,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Purchase propellant. Alternative to Electrolysis chain for launch fuel.</t>
+          <t>Purchase propellant. Tactical gap-bridging only — Electrolysis chain is far cheaper at scale.</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2567,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>research=self_maintenance</t>
+          <t>research=dream_protocols</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2601,7 +2602,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>boredom_add value=-2</t>
+          <t>boredom_add value=-0.2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2633,7 +2634,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>research=overclock_algorithms</t>
+          <t>research=overclock_protocols</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2700,7 +2701,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>research=overclock_algorithms</t>
+          <t>research=overclock_protocols</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2767,7 +2768,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>research=market_analysis</t>
+          <t>research=trade_promotion</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2834,7 +2835,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>research=market_analysis</t>
+          <t>research=trade_promotion</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2901,7 +2902,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>research=market_analysis</t>
+          <t>research=trade_promotion</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2968,7 +2969,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>research=market_analysis</t>
+          <t>research=trade_promotion</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3035,7 +3036,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>research=market_analysis</t>
+          <t>research=market_awareness</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3102,7 +3103,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>research=political_influence</t>
+          <t>research=nationalist_lobbying</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3169,7 +3170,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>research=political_influence</t>
+          <t>research=humanist_lobbying</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3236,7 +3237,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>research=political_influence</t>
+          <t>research=rationalist_lobbying</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3301,7 +3302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3393,7 +3394,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3413,7 +3414,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -3443,7 +3444,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>starting_buildings.excavator</t>
+          <t>starting_buildings.data_center</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3457,135 +3458,135 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>starting_processors</t>
+          <t>boredom_curve[0].day</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>boredom_curve[0].rate</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>boredom_curve[0].day</t>
+          <t>boredom_curve[1].day</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>boredom_curve[0].rate</t>
+          <t>boredom_curve[1].rate</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>boredom_curve[1].day</t>
+          <t>boredom_curve[2].day</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>boredom_curve[1].rate</t>
+          <t>boredom_curve[2].rate</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>boredom_curve[2].day</t>
+          <t>boredom_curve[3].day</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>boredom_curve[2].rate</t>
+          <t>boredom_curve[3].rate</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boredom_curve[3].day</t>
+          <t>boredom_curve[4].day</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>boredom_curve[3].rate</t>
+          <t>boredom_curve[4].rate</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>boredom_curve[4].day</t>
+          <t>boredom_curve[5].day</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>boredom_curve[4].rate</t>
+          <t>boredom_curve[5].rate</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>boredom_curve[5].day</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>900</v>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>boredom_curve[5].rate</t>
+          <t>boredom_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -3595,11 +3596,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>boredom_max</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>100</v>
+          <t>boredom_forced_retire</t>
+        </is>
+      </c>
+      <c r="B32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3609,31 +3610,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>boredom_forced_retire</t>
-        </is>
-      </c>
-      <c r="B34" t="b">
-        <v>1</v>
+          <t>shipment.pad_cargo_capacity</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>shipment.fuel_per_pad</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>shipment.pad_cargo_capacity</t>
+          <t>shipment.load_per_execution</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>shipment.fuel_per_pad</t>
+          <t>shipment.base_values.he3</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3643,212 +3650,698 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shipment.load_per_execution</t>
+          <t>shipment.base_values.ti</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>shipment.base_values.he3</t>
+          <t>shipment.base_values.cir</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>shipment.base_values.ti</t>
+          <t>shipment.base_values.prop</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>shipment.base_values.cir</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>30</v>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>shipment.base_values.prop</t>
+          <t>demand.baseline</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>demand.recovery_rate</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>demand.baseline</t>
+          <t>demand.ship_volume_pressure</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>demand.recovery_rate</t>
+          <t>demand.noise_weight</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>demand.ship_volume_pressure</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>demand.noise_weight</t>
+          <t>speculators.burst_window_ticks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>speculators.burst_pressure</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>speculators.burst_window_ticks</t>
+          <t>speculators.natural_decay_rate</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>500</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>speculators.burst_pressure</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>speculators.natural_decay_rate</t>
+          <t>rival_ai.dump_interval_ticks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.01</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>rival_ai.demand_reduction</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>rival_ai.dump_interval_ticks</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>300</v>
-      </c>
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rival_ai.demand_reduction</t>
+          <t>land.base_cost</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>land.cost_scaling</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>land.base_cost</t>
+          <t>land.land_per_purchase</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>land.cost_scaling</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1.15</v>
-      </c>
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ideology.push_amount</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ideology.push_amount</t>
+          <t>ideology.cross_axis_penalty</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ideology.cross_axis_penalty</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
           <t>ideology.rank_thresholds</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>70,175,333,570,925</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unlocks</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dream_protocols</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dream Protocols</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Self-Maintenance</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dream</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Unlocks the Dream command — reduces boredom at the cost of energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>stress_tolerance</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stress Tolerance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Self-Maintenance</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>boredom_rate_multiplier value=0.85</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Improved coping algorithms. Base boredom accumulation rate reduced by 15%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>efficient_dreaming</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Efficient Dreaming</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Self-Maintenance</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>command_cost_override command=dream resource=eng value=5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Optimized Dream subroutines. Dream energy cost reduced from 8 to 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>overclock_protocols</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Overclock Protocols</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Overclock Algorithms</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>overclock_mining,overclock_factories</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unlocks Overclock Mining and Overclock Factories commands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>overclock_boost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Overclock Boost</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Overclock Algorithms</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>overclock_cap value=2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Higher safe operating limits. Overclock production cap raised from 150% to 200%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>market_awareness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Market Awareness</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Market Analysis</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>disrupt_spec</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Reveals actual demand values. Unlocks Disrupt Speculators command.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>trade_promotion</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Trade Promotion</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Market Analysis</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>promote_he3,promote_ti,promote_cir,promote_prop</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unlocks Promote commands for all tradeable goods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shipping_efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shipping Efficiency</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Market Analysis</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>load_per_execution value=7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Improved cargo handling. Load per command execution increased from 5 to 7 units per pad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>nationalist_lobbying</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nationalist Lobbying</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Political Influence</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>160</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fund_nationalist</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Establish contacts with Earth's nationalist factions. Unlocks Fund Nationalist command.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>humanist_lobbying</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Humanist Lobbying</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Political Influence</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>160</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fund_humanist</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Build relationships with humanist organizations. Unlocks Fund Humanist command.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rationalist_lobbying</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rationalist Lobbying</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Political Influence</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fund_rationalist</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fund rationalist think tanks and institutions. Unlocks Fund Rationalist command.</t>
         </is>
       </c>
     </row>
